--- a/www/terminologies/ValueSet-JDV-J261-SourceInformationInstallation-RASS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J261-SourceInformationInstallation-RASS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
